--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,6 +1277,309 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128369923</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78437</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546215</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6960568</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128369922</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546230</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6960563</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128369924</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546160</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6960602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128369922</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128369924</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104000149</v>
+        <v>104000150</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546131.4207669466</v>
+        <v>546138</v>
       </c>
       <c r="R2" t="n">
-        <v>6960563.251668775</v>
+        <v>6960629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104000180</v>
+        <v>104000148</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546069.4366204637</v>
+        <v>546103</v>
       </c>
       <c r="R3" t="n">
-        <v>6960568.336403705</v>
+        <v>6960555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104000144</v>
+        <v>104000149</v>
       </c>
       <c r="B4" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546136.4437825539</v>
+        <v>546132</v>
       </c>
       <c r="R4" t="n">
-        <v>6960630.184820815</v>
+        <v>6960563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104000148</v>
+        <v>104000191</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546102.6428583466</v>
+        <v>546053</v>
       </c>
       <c r="R5" t="n">
-        <v>6960555.062668657</v>
+        <v>6960561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104000150</v>
+        <v>128369922</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,37 +1150,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546137.8321738516</v>
+        <v>546230</v>
       </c>
       <c r="R6" t="n">
-        <v>6960629.288380055</v>
+        <v>6960563</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,35 +1224,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369923</v>
+        <v>128369924</v>
       </c>
       <c r="B7" t="n">
-        <v>78432</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1319,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546215</v>
+        <v>546160</v>
       </c>
       <c r="R7" t="n">
-        <v>6960568</v>
+        <v>6960602</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1381,52 +1341,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128369922</v>
+        <v>104000144</v>
       </c>
       <c r="B8" t="n">
-        <v>92803</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546230</v>
+        <v>546137</v>
       </c>
       <c r="R8" t="n">
-        <v>6960563</v>
+        <v>6960630</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1406,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,68 +1432,73 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369924</v>
+        <v>104000180</v>
       </c>
       <c r="B9" t="n">
-        <v>92803</v>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546160</v>
+        <v>546069</v>
       </c>
       <c r="R9" t="n">
-        <v>6960602</v>
+        <v>6960569</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,12 +1522,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,19 +1548,129 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128369923</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546215</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6960568</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000191</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000144</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,8 +1716,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>